--- a/Health-Blood-Pressure/blood_pressure.xlsx
+++ b/Health-Blood-Pressure/blood_pressure.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\WrittenNotes\Health-Blood-Pressure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C41F91A-26EA-4C7C-ACFF-7FC295A70D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A29D8B6-80B4-438D-BD5F-9DD364EB220A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="September 2024" sheetId="17" r:id="rId1"/>
+    <sheet name="October 2024 - 2025" sheetId="17" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1046,7 +1046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J920"/>
+  <dimension ref="A1:J909"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.5703125" customWidth="1"/>
@@ -1272,31 +1272,32 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="17">
-        <v>45536</v>
+        <v>45582</v>
       </c>
       <c r="B17" s="18">
-        <v>264.10000000000002</v>
-      </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18">
-        <v>137</v>
-      </c>
-      <c r="G17" s="18">
-        <v>101</v>
-      </c>
-      <c r="H17" s="18">
-        <v>80</v>
-      </c>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16">
-        <v>98</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="C17" s="18">
+        <v>135</v>
+      </c>
+      <c r="D17" s="18">
+        <v>106</v>
+      </c>
+      <c r="E17" s="18">
+        <v>74</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="16">
+        <v>97</v>
+      </c>
+      <c r="J17" s="16"/>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1">
       <c r="A18" s="17">
-        <v>45537</v>
+        <f>A17+7</f>
+        <v>45589</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="18"/>
@@ -1310,7 +1311,8 @@
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1">
       <c r="A19" s="17">
-        <v>45538</v>
+        <f t="shared" ref="A19:A35" si="0">A18+7</f>
+        <v>45596</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="18"/>
@@ -1324,7 +1326,8 @@
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1">
       <c r="A20" s="17">
-        <v>45539</v>
+        <f t="shared" si="0"/>
+        <v>45603</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="18"/>
@@ -1338,7 +1341,8 @@
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="17">
-        <v>45540</v>
+        <f t="shared" si="0"/>
+        <v>45610</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="18"/>
@@ -1352,7 +1356,8 @@
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="17">
-        <v>45541</v>
+        <f t="shared" si="0"/>
+        <v>45617</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="18"/>
@@ -1366,7 +1371,8 @@
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="17">
-        <v>45542</v>
+        <f t="shared" si="0"/>
+        <v>45624</v>
       </c>
       <c r="B23" s="16"/>
       <c r="C23" s="18"/>
@@ -1380,7 +1386,8 @@
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="17">
-        <v>45543</v>
+        <f t="shared" si="0"/>
+        <v>45631</v>
       </c>
       <c r="B24" s="16"/>
       <c r="C24" s="18"/>
@@ -1394,7 +1401,8 @@
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="17">
-        <v>45544</v>
+        <f t="shared" si="0"/>
+        <v>45638</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="18"/>
@@ -1408,7 +1416,8 @@
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1">
       <c r="A26" s="17">
-        <v>45545</v>
+        <f t="shared" si="0"/>
+        <v>45645</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="18"/>
@@ -1422,7 +1431,8 @@
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1">
       <c r="A27" s="17">
-        <v>45546</v>
+        <f t="shared" si="0"/>
+        <v>45652</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="18"/>
@@ -1436,7 +1446,8 @@
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1">
       <c r="A28" s="17">
-        <v>45547</v>
+        <f t="shared" si="0"/>
+        <v>45659</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="18"/>
@@ -1450,7 +1461,8 @@
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1">
       <c r="A29" s="17">
-        <v>45548</v>
+        <f t="shared" si="0"/>
+        <v>45666</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="18"/>
@@ -1464,7 +1476,8 @@
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1">
       <c r="A30" s="17">
-        <v>45549</v>
+        <f t="shared" si="0"/>
+        <v>45673</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="18"/>
@@ -1478,7 +1491,8 @@
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1">
       <c r="A31" s="17">
-        <v>45550</v>
+        <f t="shared" si="0"/>
+        <v>45680</v>
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="18"/>
@@ -1492,7 +1506,8 @@
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1">
       <c r="A32" s="17">
-        <v>45551</v>
+        <f t="shared" si="0"/>
+        <v>45687</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="18"/>
@@ -1506,7 +1521,8 @@
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1">
       <c r="A33" s="17">
-        <v>45552</v>
+        <f t="shared" si="0"/>
+        <v>45694</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="18"/>
@@ -1520,7 +1536,8 @@
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1">
       <c r="A34" s="17">
-        <v>45553</v>
+        <f t="shared" si="0"/>
+        <v>45701</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="18"/>
@@ -1534,7 +1551,8 @@
     </row>
     <row r="35" spans="1:10" ht="15.75" customHeight="1">
       <c r="A35" s="17">
-        <v>45554</v>
+        <f t="shared" si="0"/>
+        <v>45708</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="18"/>
@@ -1546,160 +1564,17 @@
       <c r="I35" s="16"/>
       <c r="J35" s="16"/>
     </row>
-    <row r="36" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A36" s="17">
-        <v>45555</v>
-      </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-    </row>
-    <row r="37" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A37" s="17">
-        <v>45556</v>
-      </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
-    </row>
-    <row r="38" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A38" s="17">
-        <v>45557</v>
-      </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-    </row>
-    <row r="39" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A39" s="17">
-        <v>45558</v>
-      </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-    </row>
-    <row r="40" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A40" s="17">
-        <v>45559</v>
-      </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-    </row>
-    <row r="41" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A41" s="17">
-        <v>45560</v>
-      </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="16"/>
-      <c r="J41" s="16"/>
-    </row>
-    <row r="42" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A42" s="17">
-        <v>45561</v>
-      </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-    </row>
-    <row r="43" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A43" s="17">
-        <v>45562</v>
-      </c>
-      <c r="B43" s="16"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
-      <c r="J43" s="16"/>
-    </row>
-    <row r="44" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A44" s="17">
-        <v>45563</v>
-      </c>
-      <c r="B44" s="16"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
-    </row>
-    <row r="45" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A45" s="17">
-        <v>45564</v>
-      </c>
-      <c r="B45" s="16"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="16"/>
-      <c r="J45" s="16"/>
-    </row>
-    <row r="46" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A46" s="17">
-        <v>45565</v>
-      </c>
-      <c r="B46" s="16"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="16"/>
-      <c r="I46" s="16"/>
-      <c r="J46" s="16"/>
-    </row>
+    <row r="36" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:10" ht="15.75" customHeight="1"/>
     <row r="47" spans="1:10" ht="15.75" customHeight="1"/>
     <row r="48" spans="1:10" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
@@ -2563,17 +2438,6 @@
     <row r="907" ht="15.75" customHeight="1"/>
     <row r="908" ht="15.75" customHeight="1"/>
     <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="I16:J16"/>
@@ -2588,7 +2452,7 @@
     <mergeCell ref="F5:H8"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="C17:C46 F17:F46">
+  <conditionalFormatting sqref="C17:C35 F17:F35">
     <cfRule type="cellIs" dxfId="33" priority="1251" operator="lessThan">
       <formula>120</formula>
     </cfRule>
@@ -2644,7 +2508,7 @@
       <formula>120</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D17:D46 G17:G46">
+  <conditionalFormatting sqref="D17:D35 G17:G35">
     <cfRule type="cellIs" dxfId="15" priority="859" operator="between">
       <formula>80</formula>
       <formula>90</formula>
